--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -515,58 +515,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>28.19</v>
       </c>
-      <c r="E2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>29.28</v>
       </c>
-      <c r="H2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>26.99</v>
       </c>
-      <c r="K2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="K2" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>24.5</v>
+        <v>24.31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>24.8</v>
@@ -586,7 +586,7 @@
         <v>23.56</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>24.52</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>22.48</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -627,58 +627,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E4" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="H4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>19.67</v>
       </c>
-      <c r="K4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="K4" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.39</v>
+        <v>6.7</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.82</v>
       </c>
       <c r="E5" t="n">
-        <v>53.7</v>
+        <v>46.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>10.25</v>
       </c>
       <c r="H5" t="n">
-        <v>60.4</v>
+        <v>53</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>46.5</v>
+        <v>39.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>25.88</v>
+        <v>26.35</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
@@ -530,7 +530,7 @@
         <v>28.19</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
         <v>29.28</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13.1</v>
+        <v>11.1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         <v>26.99</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>24.31</v>
+        <v>25.51</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>24.8</v>
@@ -586,18 +586,18 @@
         <v>23.56</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3.1</v>
+        <v>-7.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>24.52</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.9</v>
+        <v>-3.9</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>22.48</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-7.5</v>
+        <v>-11.9</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>19.08</v>
+        <v>19.07</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>27.98</v>
@@ -642,7 +642,7 @@
         <v>20.34</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>20.95</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.82</v>
       </c>
       <c r="E5" t="n">
-        <v>46.6</v>
+        <v>42.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>10.25</v>
       </c>
       <c r="H5" t="n">
-        <v>53</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>39.7</v>
+        <v>35.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -521,38 +521,38 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>26.35</v>
+        <v>26.54</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.19</v>
+        <v>27.69</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>26.99</v>
+        <v>26.53</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.4</v>
+        <v>-0.1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+          <t>HOLD under Set A/Set C; BUY under Set B</t>
         </is>
       </c>
     </row>
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>25.51</v>
+        <v>25.35</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>24.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23.56</v>
+        <v>23.15</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-7.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24.52</v>
+        <v>24.09</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-3.9</v>
+        <v>-5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22.48</v>
+        <v>22.11</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-11.9</v>
+        <v>-12.8</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -633,38 +633,38 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>19.07</v>
+        <v>19.56</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>27.98</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20.34</v>
+        <v>20.1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="n">
-        <v>19.67</v>
+        <v>19.44</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3.1</v>
+        <v>-0.6</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+          <t>HOLD under Set A/Set C; BUY under Set B</t>
         </is>
       </c>
     </row>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.82</v>
+        <v>9.56</v>
       </c>
       <c r="E5" t="n">
-        <v>42.3</v>
+        <v>37.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10.25</v>
+        <v>9.98</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>43.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.359999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>35.7</v>
+        <v>31</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -735,6 +735,62 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>position BUY across all 3 weight sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>26.54</v>
+        <v>26.56</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
@@ -571,114 +571,114 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="C3" t="n">
         <v>24.8</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>23.15</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" t="n">
         <v>24.09</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
+      <c r="H3" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>22.11</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="C4" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>20.1</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" t="n">
         <v>20.7</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>19.44</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A/Set C; BUY under Set B</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.96</v>
+        <v>7.13</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.56</v>
       </c>
       <c r="E5" t="n">
-        <v>37.4</v>
+        <v>34.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.98</v>
       </c>
       <c r="H5" t="n">
-        <v>43.4</v>
+        <v>40</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>27.9</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.39</v>
+        <v>0.3905</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.443</v>
@@ -754,7 +754,7 @@
         <v>0.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>0.39</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.37</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -515,170 +515,170 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>26.56</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>27.69</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="E2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>28.75</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>26.53</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A/Set C; BUY under Set B</t>
+      <c r="K2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>position BUY across all 3 weight sets</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="2" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>23.15</v>
       </c>
-      <c r="E3" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 3 weight sets</t>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>position HOLD across all 3 weight sets</t>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.13</v>
+        <v>6.82</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.56</v>
       </c>
       <c r="E5" t="n">
-        <v>34.1</v>
+        <v>40.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.98</v>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
+        <v>46.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>27.9</v>
+        <v>33.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3905</v>
+        <v>0.3955</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.443</v>
@@ -754,7 +754,7 @@
         <v>0.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-3.3</v>
+        <v>-4.6</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>0.39</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-1.1</v>
+        <v>-2.4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.37</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-5.7</v>
+        <v>-6.9</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -527,10 +527,10 @@
         <v>34.5</v>
       </c>
       <c r="D2" t="n">
-        <v>27.69</v>
+        <v>28.35</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2</v>
+        <v>13.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28.75</v>
+        <v>29.43</v>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>18.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>26.53</v>
+        <v>27.16</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         <v>24.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23.15</v>
+        <v>23.82</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-4</v>
+        <v>-1.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24.09</v>
+        <v>24.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-0.1</v>
+        <v>2.7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22.11</v>
+        <v>22.75</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-8.4</v>
+        <v>-5.7</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -627,58 +627,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>18.81</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+      <c r="J4" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>position BUY across all 3 weight sets</t>
         </is>
       </c>
     </row>
@@ -695,10 +695,10 @@
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="E5" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.98</v>
+        <v>10.02</v>
       </c>
       <c r="H5" t="n">
-        <v>46.3</v>
+        <v>46.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.119999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="K5" t="n">
-        <v>33.7</v>
+        <v>34.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>0.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-4.6</v>
+        <v>-2.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>0.39</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>-2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.37</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-6.9</v>
+        <v>-5.2</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -695,10 +695,10 @@
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.6</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10.02</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>46.9</v>
+        <v>45</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.15</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>34.2</v>
+        <v>32.4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -515,58 +515,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>28.35</v>
       </c>
-      <c r="E2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>29.43</v>
       </c>
-      <c r="H2" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>27.16</v>
       </c>
-      <c r="K2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="K2" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>24.12</v>
+        <v>25.26</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>24.8</v>
@@ -586,18 +586,18 @@
         <v>23.82</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1.2</v>
+        <v>-5.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>24.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.7</v>
+        <v>-1.9</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>22.75</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-5.7</v>
+        <v>-9.9</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.81</v>
+        <v>18.63</v>
       </c>
       <c r="C4" t="n">
         <v>27.98</v>
@@ -642,7 +642,7 @@
         <v>20.55</v>
       </c>
       <c r="E4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>21.16</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>19.87</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.82</v>
+        <v>7.16</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>38.9</v>
+        <v>32.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>38.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>32.4</v>
+        <v>26.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -739,58 +739,58 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0.3955</v>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.443</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>0.38</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" t="n">
         <v>0.39</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" t="n">
         <v>0.37</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+      <c r="K6" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -29,17 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE6E6"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,114 +509,114 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="C2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+      <c r="G2" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="C3" t="n">
         <v>24.8</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>23.82</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
+      <c r="J3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>
@@ -633,16 +627,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.63</v>
+        <v>18.84</v>
       </c>
       <c r="C4" t="n">
         <v>27.98</v>
       </c>
       <c r="D4" t="n">
-        <v>20.55</v>
+        <v>20.47</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,10 +644,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.16</v>
+        <v>21.07</v>
       </c>
       <c r="H4" t="n">
-        <v>13.6</v>
+        <v>11.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -661,10 +655,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19.87</v>
+        <v>19.8</v>
       </c>
       <c r="K4" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,16 +683,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.16</v>
+        <v>7.67</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.470000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="E5" t="n">
-        <v>32.3</v>
+        <v>22.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +700,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="H5" t="n">
-        <v>38.1</v>
+        <v>28.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +711,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.029999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="K5" t="n">
-        <v>26.2</v>
+        <v>17.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +739,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3941</v>
+        <v>0.4208</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,33 +748,33 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0.39</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2</v>
+        <v>-6.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.37</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.9</v>
+        <v>-11.3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -790,7 +784,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>position HOLD across all 3 weight sets</t>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -29,12 +29,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6E6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,58 +515,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>28.14</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="2" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>29.26</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G2" s="2" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>position HOLD across all 3 weight sets</t>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A/Set C; BUY under Set B</t>
         </is>
       </c>
     </row>
@@ -577,10 +583,10 @@
         <v>24.8</v>
       </c>
       <c r="D3" t="n">
-        <v>23.66</v>
+        <v>24.08</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.6</v>
+        <v>-10.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -588,10 +594,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24.61</v>
+        <v>25.04</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.1</v>
+        <v>-6.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -599,10 +605,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.6</v>
+        <v>-14.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -633,10 +639,10 @@
         <v>27.98</v>
       </c>
       <c r="D4" t="n">
-        <v>20.47</v>
+        <v>20.79</v>
       </c>
       <c r="E4" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -644,10 +650,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.07</v>
+        <v>21.4</v>
       </c>
       <c r="H4" t="n">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -655,10 +661,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19.8</v>
+        <v>20.11</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,10 +695,10 @@
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.42</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -700,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.83</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -711,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>17.1</v>
+        <v>17.8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,32 +751,32 @@
         <v>0.443</v>
       </c>
       <c r="D6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0.38</v>
       </c>
-      <c r="E6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.37</v>
-      </c>
       <c r="K6" t="n">
-        <v>-11.3</v>
+        <v>-10</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -515,170 +515,170 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="C2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>28.62</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" t="n">
         <v>29.71</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="H2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>27.44</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD under Set A/Set C; BUY under Set B</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="2" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>24.08</v>
       </c>
-      <c r="E3" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>25.04</v>
       </c>
-      <c r="H3" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>23</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>position TRIM/SHORT across all 3 weight sets</t>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>18.84</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>19.305</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="H4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>20.11</v>
       </c>
-      <c r="K4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="K4" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.67</v>
+        <v>7.81</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4208</v>
+        <v>0.4183</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,7 +754,7 @@
         <v>0.39</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.8</v>
+        <v>-7.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.6</v>
+        <v>-5.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.38</v>
       </c>
       <c r="K6" t="n">
-        <v>-10</v>
+        <v>-9.5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -695,10 +695,10 @@
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.470000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="E5" t="n">
-        <v>21.3</v>
+        <v>29.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.880000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H5" t="n">
-        <v>26.6</v>
+        <v>34.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.029999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="K5" t="n">
-        <v>15.6</v>
+        <v>23.9</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -515,58 +515,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SBLK</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>28.77</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>28.62</v>
       </c>
-      <c r="E2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>29.71</v>
       </c>
-      <c r="H2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>27.44</v>
       </c>
-      <c r="K2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>position HOLD across all 3 weight sets</t>
+      <c r="K2" s="2" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>25.76</v>
+        <v>25.33</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>24.8</v>
@@ -586,18 +586,18 @@
         <v>24.08</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-6.5</v>
+        <v>-4.9</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>25.04</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-10.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -622,63 +622,63 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>19.305</v>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C4" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>20.79</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" t="n">
         <v>21.4</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" t="n">
         <v>20.11</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>position BUY across all 3 weight sets</t>
         </is>
       </c>
     </row>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.81</v>
+        <v>7.6</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>10.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>29.4</v>
+        <v>24.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>34.5</v>
+        <v>30.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.68</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>23.9</v>
+        <v>18.8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4183</v>
+        <v>0.4845</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,7 +754,7 @@
         <v>0.39</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.2</v>
+        <v>-19.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.1</v>
+        <v>-18</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.38</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.5</v>
+        <v>-21.9</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.029999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -583,32 +583,32 @@
         <v>24.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>24.08</v>
+        <v>23.42</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-4.9</v>
+        <v>-7.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>25.04</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="J3" s="2" t="n">
-        <v>23</v>
+        <v>22.33</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11.8</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -751,32 +751,32 @@
         <v>0.443</v>
       </c>
       <c r="D6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>0.39</v>
       </c>
-      <c r="E6" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.38</v>
-      </c>
       <c r="K6" t="n">
-        <v>-21.9</v>
+        <v>-19.5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -527,10 +527,10 @@
         <v>34.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.62</v>
+        <v>30.22</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1</v>
+        <v>4.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -538,27 +538,27 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29.71</v>
+        <v>31.32</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>27.44</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+          <t>HOLD under Set A/Set C; BUY under Set B</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -639,10 +639,10 @@
         <v>27.98</v>
       </c>
       <c r="D4" t="n">
-        <v>20.79</v>
+        <v>20.33</v>
       </c>
       <c r="E4" t="n">
-        <v>16.8</v>
+        <v>14.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21.4</v>
+        <v>20.93</v>
       </c>
       <c r="H4" t="n">
-        <v>20.2</v>
+        <v>17.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>20.11</v>
+        <v>19.66</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -521,44 +521,44 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>28.9</v>
+        <v>27.89</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>30.22</v>
+        <v>29.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>30.86</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>31.32</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>WEIGHT-DRIVEN</t>
@@ -566,63 +566,63 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set C; BUY under Set B</t>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>GNK</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="C3" t="n">
         <v>24.8</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>TRIM/SHORT</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>WEIGHT-DRIVEN</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
+      <c r="J3" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>WEIGHT-ROBUST</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.8</v>
+        <v>17.68</v>
       </c>
       <c r="C4" t="n">
         <v>27.98</v>
       </c>
       <c r="D4" t="n">
-        <v>20.33</v>
+        <v>20.11</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20.93</v>
+        <v>20.7</v>
       </c>
       <c r="H4" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19.66</v>
+        <v>19.45</v>
       </c>
       <c r="K4" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.6</v>
+        <v>7.46</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9.470000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>24.6</v>
+        <v>27.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9.869999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="H5" t="n">
-        <v>29.8</v>
+        <v>33</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>22.3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4845</v>
+        <v>0.39</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,33 +754,33 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-17.5</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-15.6</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-19.5</v>
+        <v>-1.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>position TRIM/SHORT across all 3 weight sets</t>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>27.89</v>
+        <v>29.05</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
@@ -530,18 +530,18 @@
         <v>29.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>30.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.7</v>
+        <v>6.2</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         <v>28.61</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.6</v>
+        <v>-1.5</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>BUY under Set A/Set B; HOLD under Set C</t>
+          <t>HOLD under Set A/Set C; BUY under Set B</t>
         </is>
       </c>
     </row>
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.26</v>
+        <v>26.34</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="D3" t="n">
         <v>22.67</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.2</v>
+        <v>-13.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>23.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.6</v>
+        <v>-10.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>21.63</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.4</v>
+        <v>-17.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.68</v>
+        <v>18.23</v>
       </c>
       <c r="C4" t="n">
         <v>27.98</v>
@@ -642,7 +642,7 @@
         <v>20.11</v>
       </c>
       <c r="E4" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>20.7</v>
       </c>
       <c r="H4" t="n">
-        <v>17.1</v>
+        <v>13.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>19.45</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.46</v>
+        <v>7.75</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>27.8</v>
+        <v>23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.92</v>
       </c>
       <c r="H5" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>22.3</v>
+        <v>17.7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.39</v>
+        <v>0.4951</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,33 +754,33 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>-20.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>-18.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1</v>
+        <v>-22.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>position HOLD across all 3 weight sets</t>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>29.05</v>
+        <v>31.11</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
@@ -530,7 +530,7 @@
         <v>29.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.5</v>
+        <v>-4.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -541,22 +541,22 @@
         <v>30.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
         <v>28.61</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-1.5</v>
+        <v>-8</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set C; BUY under Set B</t>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.34</v>
+        <v>27.32</v>
       </c>
       <c r="C3" t="n">
         <v>28.4</v>
@@ -586,7 +586,7 @@
         <v>22.67</v>
       </c>
       <c r="E3" t="n">
-        <v>-13.9</v>
+        <v>-17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>23.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.4</v>
+        <v>-13.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>21.63</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.9</v>
+        <v>-20.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -627,58 +627,58 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CMDB</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>18.23</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>27.98</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>20.11</v>
       </c>
-      <c r="E4" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="E4" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>20.7</v>
       </c>
-      <c r="H4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="H4" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>19.45</v>
       </c>
-      <c r="K4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="K4" s="2" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.75</v>
+        <v>6.39</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>49.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.92</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>55.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>17.7</v>
+        <v>42.8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4951</v>
+        <v>0.39</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,33 +754,33 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-20.2</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-18.4</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-22.1</v>
+        <v>-1.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>position TRIM/SHORT across all 3 weight sets</t>
+          <t>position HOLD across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>31.11</v>
+        <v>30.48</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34.5</v>
@@ -530,7 +530,7 @@
         <v>29.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-4.2</v>
+        <v>-2.3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
         <v>30.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         <v>28.61</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-8</v>
+        <v>-6.1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.32</v>
+        <v>25.88</v>
       </c>
       <c r="C3" t="n">
         <v>28.4</v>
@@ -586,7 +586,7 @@
         <v>22.67</v>
       </c>
       <c r="E3" t="n">
-        <v>-17</v>
+        <v>-12.4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>23.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-13.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>21.63</v>
       </c>
       <c r="K3" t="n">
-        <v>-20.8</v>
+        <v>-16.4</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20.6</v>
+        <v>20.52</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>27.98</v>
@@ -642,7 +642,7 @@
         <v>20.11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>20.7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>19.45</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-5.6</v>
+        <v>-5.2</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -427,7 +427,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -580,7 +580,7 @@
         <v>25.88</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
       <c r="D3" t="n">
         <v>22.67</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.39</v>
+        <v>8.52</v>
       </c>
       <c r="C5" t="n">
         <v>7.1</v>
@@ -698,7 +698,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>49.2</v>
+        <v>11.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>9.92</v>
       </c>
       <c r="H5" t="n">
-        <v>55.2</v>
+        <v>16.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>42.8</v>
+        <v>7.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.39</v>
+        <v>0.5326</v>
       </c>
       <c r="C6" t="n">
         <v>0.443</v>
@@ -754,33 +754,33 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>-25.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>-24.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>0.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1</v>
+        <v>-27.6</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>TRIM/SHORT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>position HOLD across all 3 weight sets</t>
+          <t>position TRIM/SHORT across all 3 weight sets</t>
         </is>
       </c>
     </row>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -527,32 +527,32 @@
         <v>34.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.79</v>
+        <v>28.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-2.3</v>
+        <v>-5.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>TRIM/SHORT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>30.86</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>28.61</v>
+        <v>27.64</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-6.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>HOLD under Set A/Set B; TRIM/SHORT under Set C</t>
+          <t>TRIM/SHORT under Set A/Set C; HOLD under Set B</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         <v>27.2</v>
       </c>
       <c r="D3" t="n">
-        <v>22.67</v>
+        <v>21.66</v>
       </c>
       <c r="E3" t="n">
-        <v>-12.4</v>
+        <v>-16.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23.6</v>
+        <v>22.52</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.800000000000001</v>
+        <v>-13</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21.63</v>
+        <v>20.69</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.4</v>
+        <v>-20.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         <v>27.98</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20.11</v>
+        <v>19.53</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-2</v>
+        <v>-4.8</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20.7</v>
+        <v>20.08</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.45</v>
+        <v>18.91</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-5.2</v>
+        <v>-7.8</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -683,58 +683,58 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>8.52</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="2" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="H5" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>WEIGHT-ROBUST</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>position BUY across all 3 weight sets</t>
+      <c r="J5" s="2" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>WEIGHT-DRIVEN</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>BUY under Set A/Set B; HOLD under Set C</t>
         </is>
       </c>
     </row>
@@ -751,10 +751,10 @@
         <v>0.443</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>-25.8</v>
+        <v>-29.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H6" t="n">
-        <v>-24.1</v>
+        <v>-27.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="K6" t="n">
-        <v>-27.6</v>
+        <v>-30.9</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>

--- a/outputs/dry_bulk_weight_robustness.xlsx
+++ b/outputs/dry_bulk_weight_robustness.xlsx
@@ -527,10 +527,10 @@
         <v>34.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.74</v>
+        <v>28.59</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29.75</v>
+        <v>29.58</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>27.64</v>
+        <v>27.51</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         <v>27.2</v>
       </c>
       <c r="D3" t="n">
-        <v>21.66</v>
+        <v>21.45</v>
       </c>
       <c r="E3" t="n">
-        <v>-16.3</v>
+        <v>-17.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22.52</v>
+        <v>22.29</v>
       </c>
       <c r="H3" t="n">
-        <v>-13</v>
+        <v>-13.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>20.69</v>
+        <v>20.51</v>
       </c>
       <c r="K3" t="n">
-        <v>-20.1</v>
+        <v>-20.8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         <v>27.98</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19.53</v>
+        <v>19.51</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20.08</v>
+        <v>20.06</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>18.91</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-7.8</v>
+        <v>-7.9</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -695,10 +695,10 @@
         <v>7.1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.85</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>-29.2</v>
+        <v>-29.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H6" t="n">
-        <v>-27.7</v>
+        <v>-27.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.37</v>
       </c>
       <c r="K6" t="n">
-        <v>-30.9</v>
+        <v>-31.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
